--- a/sample_data/fixed_data/fix_preview.xlsx
+++ b/sample_data/fixed_data/fix_preview.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="修复预览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="__ecommerce_checker__" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,40 +414,138 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>商品编码</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>标题</t>
+          <t>修改字段</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>错误信息</t>
+          <t>原值</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>新值</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>修改原因</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>PROD002</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>假数据</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>这是模拟报告文件，不应被读取</t>
+          <t>这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>标题长度为 160 字符，超过最大限制 60 字符</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PROD003</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>高仿奢侈品包包原单复刻爆款</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>高仿奢侈品包包原单复刻</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>标题包含敏感词: 爆款</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PROD005</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>服装</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>商品类目为空</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>marker</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ecommerce_checker_tool_generated</t>
         </is>
       </c>
     </row>

--- a/sample_data/fixed_data/fix_preview.xlsx
+++ b/sample_data/fixed_data/fix_preview.xlsx
@@ -462,12 +462,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个</t>
+          <t>这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是一个超长标题这是</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>标题长度为 160 字符，超过最大限制 60 字符</t>
+          <t>标题长度为 160 字符，超过最大限制 50 字符</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>标题包含敏感词: 爆款</t>
+          <t>标题包含敏感词: 爆款, 爆款</t>
         </is>
       </c>
     </row>
